--- a/data/suppliers/xado-code-map.xlsx
+++ b/data/suppliers/xado-code-map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc_user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\maintenance-503\data\suppliers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5503A3F2-1FAF-4EAD-8CD1-A3A7758B490D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B09721-4135-47D7-93C7-DF84CFCAA5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24225" yWindow="3270" windowWidth="25320" windowHeight="16950" xr2:uid="{BCE9FDD1-F8EA-4C69-AD82-1CBF913DB0E1}"/>
+    <workbookView xWindow="2730" yWindow="900" windowWidth="13950" windowHeight="14580" xr2:uid="{BCE9FDD1-F8EA-4C69-AD82-1CBF913DB0E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
